--- a/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\TEAM PJT JM 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\TEAM PJT JM 2\Ssafy_We_Are\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{575958D9-E75F-4624-BD48-8773A9DAFE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985985A1-CC80-4B01-9D5D-153FD71FEC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1395" yWindow="1335" windowWidth="18240" windowHeight="15345" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3750" yWindow="1485" windowWidth="18240" windowHeight="15345" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,17 @@
     <sheet name="5_WBS_간트차트(실습)" sheetId="6" r:id="rId6"/>
     <sheet name="6_용어설명(참고)" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -31,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="300">
   <si>
     <t>실습 소재</t>
   </si>
@@ -10956,9 +10965,6 @@
     <t>화면(UI) 및 와이어프레임 설계</t>
   </si>
   <si>
-    <t>FE</t>
-  </si>
-  <si>
     <t>공공데이터(JSON) 및 지도 구조 설계</t>
   </si>
   <si>
@@ -10990,6 +10996,28 @@
   </si>
   <si>
     <t>발표 PPT 제작 및 시연 리허설</t>
+  </si>
+  <si>
+    <t>김지명</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>전준혁</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>정용철</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>팀전체</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
+  </si>
+  <si>
+    <t>진행중</t>
   </si>
 </sst>
 </file>
@@ -11588,6 +11616,19 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -11634,13 +11675,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11655,29 +11699,14 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -11715,29 +11744,28 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12031,10 +12059,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="47"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="14" t="s">
@@ -12069,10 +12097,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="39"/>
+      <c r="C9" s="44"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -12123,28 +12151,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="41"/>
+      <c r="C17" s="46"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="44"/>
+      <c r="C18" s="49"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="37"/>
+      <c r="C19" s="42"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="37"/>
+      <c r="C20" s="42"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -12178,13 +12206,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -12276,46 +12304,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="54" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="39"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="44"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12348,22 +12376,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="56" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="39"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="44"/>
     </row>
     <row r="4" spans="2:6" ht="35.65" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -12910,37 +12938,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="2:8" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="39"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="44"/>
     </row>
     <row r="4" spans="2:8" ht="18" customHeight="1">
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="39"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="44"/>
     </row>
     <row r="5" spans="2:8" ht="31.5" customHeight="1">
       <c r="B5" s="10" t="s">
@@ -12990,7 +13018,7 @@
       </c>
     </row>
     <row r="7" spans="2:8" s="28" customFormat="1" ht="38.25">
-      <c r="B7" s="88" t="s">
+      <c r="B7" s="39" t="s">
         <v>273</v>
       </c>
       <c r="C7" s="12" t="s">
@@ -13009,7 +13037,7 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="H7" s="85" t="s">
+      <c r="H7" s="38" t="s">
         <v>266</v>
       </c>
     </row>
@@ -13057,7 +13085,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="H9" s="85" t="s">
+      <c r="H9" s="38" t="s">
         <v>263</v>
       </c>
     </row>
@@ -13081,7 +13109,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="H10" s="85" t="s">
+      <c r="H10" s="38" t="s">
         <v>263</v>
       </c>
     </row>
@@ -13105,7 +13133,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="H11" s="85" t="s">
+      <c r="H11" s="38" t="s">
         <v>266</v>
       </c>
     </row>
@@ -13129,7 +13157,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="H12" s="85" t="s">
+      <c r="H12" s="38" t="s">
         <v>269</v>
       </c>
     </row>
@@ -13153,7 +13181,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="H13" s="85" t="s">
+      <c r="H13" s="38" t="s">
         <v>269</v>
       </c>
     </row>
@@ -13177,7 +13205,7 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="H14" s="85" t="s">
+      <c r="H14" s="38" t="s">
         <v>266</v>
       </c>
     </row>
@@ -13201,7 +13229,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="H15" s="85" t="s">
+      <c r="H15" s="38" t="s">
         <v>266</v>
       </c>
     </row>
@@ -13257,14 +13285,14 @@
       <c r="B21" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="87" t="s">
+      <c r="C21" s="59" t="s">
         <v>277</v>
       </c>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="86"/>
-      <c r="G21" s="86"/>
-      <c r="H21" s="41"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -13309,22 +13337,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="48"/>
+      <c r="C2" s="53"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="39"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="81" t="s">
+      <c r="C4" s="36" t="s">
         <v>232</v>
       </c>
     </row>
@@ -13353,163 +13381,167 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="55"/>
+      <c r="C9" s="68"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="82" t="s">
+      <c r="B10" s="61" t="s">
         <v>236</v>
       </c>
-      <c r="C10" s="44"/>
+      <c r="C10" s="49"/>
     </row>
     <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="48" t="s">
         <v>237</v>
       </c>
-      <c r="C11" s="44"/>
+      <c r="C11" s="49"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="82" t="s">
+      <c r="B12" s="61" t="s">
         <v>238</v>
       </c>
-      <c r="C12" s="44"/>
+      <c r="C12" s="49"/>
     </row>
     <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="48" t="s">
         <v>239</v>
       </c>
-      <c r="C13" s="44"/>
+      <c r="C13" s="49"/>
     </row>
     <row r="14" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="C14" s="44"/>
+      <c r="C14" s="49"/>
     </row>
     <row r="15" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B15" s="82" t="s">
+      <c r="B15" s="61" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="44"/>
+      <c r="C15" s="49"/>
     </row>
     <row r="16" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="48" t="s">
         <v>242</v>
       </c>
-      <c r="C16" s="44"/>
+      <c r="C16" s="49"/>
     </row>
     <row r="17" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A17" s="83"/>
-      <c r="B17" s="43" t="s">
+      <c r="A17" s="37"/>
+      <c r="B17" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="C17" s="44"/>
+      <c r="C17" s="49"/>
     </row>
     <row r="18" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B18" s="82" t="s">
+      <c r="B18" s="61" t="s">
         <v>244</v>
       </c>
-      <c r="C18" s="44"/>
+      <c r="C18" s="49"/>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1">
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="60"/>
+      <c r="C20" s="66"/>
     </row>
     <row r="21" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B21" s="82" t="s">
+      <c r="B21" s="61" t="s">
         <v>245</v>
       </c>
-      <c r="C21" s="44"/>
+      <c r="C21" s="49"/>
     </row>
     <row r="22" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B22" s="82" t="s">
+      <c r="B22" s="61" t="s">
         <v>246</v>
       </c>
-      <c r="C22" s="44"/>
+      <c r="C22" s="49"/>
     </row>
     <row r="23" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B23" s="82" t="s">
+      <c r="B23" s="61" t="s">
         <v>247</v>
       </c>
-      <c r="C23" s="44"/>
+      <c r="C23" s="49"/>
     </row>
     <row r="24" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B24" s="82" t="s">
+      <c r="B24" s="61" t="s">
         <v>248</v>
       </c>
-      <c r="C24" s="44"/>
+      <c r="C24" s="49"/>
     </row>
     <row r="25" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B25" s="82" t="s">
+      <c r="B25" s="61" t="s">
         <v>250</v>
       </c>
-      <c r="C25" s="84"/>
+      <c r="C25" s="62"/>
     </row>
     <row r="26" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B26" s="82" t="s">
+      <c r="B26" s="61" t="s">
         <v>249</v>
       </c>
-      <c r="C26" s="44"/>
+      <c r="C26" s="49"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1">
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="58"/>
+      <c r="C28" s="64"/>
     </row>
     <row r="29" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B29" s="82" t="s">
+      <c r="B29" s="61" t="s">
         <v>251</v>
       </c>
-      <c r="C29" s="44"/>
+      <c r="C29" s="49"/>
     </row>
     <row r="30" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B30" s="82" t="s">
+      <c r="B30" s="61" t="s">
         <v>252</v>
       </c>
-      <c r="C30" s="44"/>
+      <c r="C30" s="49"/>
     </row>
     <row r="31" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B31" s="82" t="s">
+      <c r="B31" s="61" t="s">
         <v>254</v>
       </c>
-      <c r="C31" s="84"/>
+      <c r="C31" s="62"/>
     </row>
     <row r="32" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B32" s="82" t="s">
+      <c r="B32" s="61" t="s">
         <v>255</v>
       </c>
-      <c r="C32" s="84"/>
+      <c r="C32" s="62"/>
     </row>
     <row r="33" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B33" s="82" t="s">
+      <c r="B33" s="61" t="s">
         <v>256</v>
       </c>
-      <c r="C33" s="84"/>
+      <c r="C33" s="62"/>
     </row>
     <row r="34" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B34" s="82" t="s">
+      <c r="B34" s="61" t="s">
         <v>257</v>
       </c>
-      <c r="C34" s="84"/>
+      <c r="C34" s="62"/>
     </row>
     <row r="35" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B35" s="82" t="s">
+      <c r="B35" s="61" t="s">
         <v>253</v>
       </c>
-      <c r="C35" s="44"/>
+      <c r="C35" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
@@ -13523,15 +13555,11 @@
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13561,36 +13589,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="39"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="44"/>
     </row>
     <row r="4" spans="2:13" ht="25.5" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -13652,8 +13680,12 @@
       <c r="H5" s="5">
         <v>1</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="I5" s="5">
+        <v>100</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>298</v>
+      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -13669,7 +13701,7 @@
         <v>281</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="F6" s="5">
         <v>1</v>
@@ -13680,8 +13712,12 @@
       <c r="H6" s="5">
         <v>1</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+      <c r="I6" s="5">
+        <v>100</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>298</v>
+      </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -13697,7 +13733,7 @@
         <v>282</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F7" s="5">
         <v>1</v>
@@ -13708,8 +13744,12 @@
       <c r="H7" s="5">
         <v>1</v>
       </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+      <c r="I7" s="5">
+        <v>60</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>299</v>
+      </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -13722,10 +13762,10 @@
         <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -13736,8 +13776,12 @@
       <c r="H8" s="5">
         <v>1</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="I8" s="5">
+        <v>60</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>299</v>
+      </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -13750,10 +13794,10 @@
         <v>60</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="F9" s="5">
         <v>2</v>
@@ -13778,10 +13822,10 @@
         <v>60</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="F10" s="5">
         <v>2</v>
@@ -13806,10 +13850,10 @@
         <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="F11" s="5">
         <v>2</v>
@@ -13834,10 +13878,10 @@
         <v>60</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="F12" s="5">
         <v>2</v>
@@ -13862,10 +13906,10 @@
         <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="F13" s="5">
         <v>2</v>
@@ -13886,14 +13930,14 @@
       <c r="B14" s="5">
         <v>10</v>
       </c>
-      <c r="C14" s="89" t="s">
+      <c r="C14" s="40" t="s">
         <v>278</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="F14" s="5">
         <v>2</v>
@@ -13918,10 +13962,10 @@
         <v>61</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="F15" s="5">
         <v>3</v>
@@ -13946,7 +13990,7 @@
         <v>62</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>280</v>
@@ -13974,10 +14018,10 @@
         <v>63</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>294</v>
       </c>
       <c r="F17" s="5">
         <v>3</v>
@@ -14002,7 +14046,7 @@
         <v>64</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>280</v>
@@ -14026,72 +14070,72 @@
       <c r="D19" s="28"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="63" t="s">
+      <c r="B20" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="64"/>
+      <c r="C20" s="85"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="65" t="s">
+      <c r="B21" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="66"/>
+      <c r="C21" s="87"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="68"/>
+      <c r="C22" s="89"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="71" t="s">
+      <c r="B23" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="72"/>
+      <c r="C23" s="73"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="73" t="s">
+      <c r="B24" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="74"/>
+      <c r="C24" s="75"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="76"/>
+      <c r="C25" s="77"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="77" t="s">
+      <c r="B26" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="78"/>
+      <c r="C26" s="79"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="79" t="s">
+      <c r="B27" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="80"/>
+      <c r="C27" s="81"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="69" t="s">
+      <c r="B28" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="70"/>
+      <c r="C28" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">
@@ -14124,16 +14168,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="48"/>
+      <c r="C2" s="53"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="39"/>
+      <c r="C3" s="44"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">

--- a/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\TEAM PJT JM 2\Ssafy_We_Are\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985985A1-CC80-4B01-9D5D-153FD71FEC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C872331-7283-4AC7-9995-7B03AF0AB24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3750" yWindow="1485" windowWidth="18240" windowHeight="15345" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3750" yWindow="1485" windowWidth="18240" windowHeight="15345" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="299">
   <si>
     <t>실습 소재</t>
   </si>
@@ -10968,9 +10968,6 @@
     <t>공공데이터(JSON) 및 지도 구조 설계</t>
   </si>
   <si>
-    <t>안전 지도(CCTV·경찰관서) 구현</t>
-  </si>
-  <si>
     <t>안전 경로 추천(최단/최고 안전) 구현</t>
   </si>
   <si>
@@ -11017,7 +11014,55 @@
     <t>완료</t>
   </si>
   <si>
-    <t>진행중</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(CCTV) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -11681,7 +11726,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11699,14 +11753,29 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -11742,30 +11811,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13343,7 +13388,7 @@
       <c r="C2" s="53"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="64" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="44"/>
@@ -13381,13 +13426,13 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="68"/>
+      <c r="C9" s="62"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="63" t="s">
         <v>236</v>
       </c>
       <c r="C10" s="49"/>
@@ -13399,7 +13444,7 @@
       <c r="C11" s="49"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="63" t="s">
         <v>238</v>
       </c>
       <c r="C12" s="49"/>
@@ -13417,7 +13462,7 @@
       <c r="C14" s="49"/>
     </row>
     <row r="15" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="63" t="s">
         <v>241</v>
       </c>
       <c r="C15" s="49"/>
@@ -13436,103 +13481,114 @@
       <c r="C17" s="49"/>
     </row>
     <row r="18" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="63" t="s">
         <v>244</v>
       </c>
       <c r="C18" s="49"/>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1">
-      <c r="B20" s="65" t="s">
+      <c r="B20" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="66"/>
+      <c r="C20" s="69"/>
     </row>
     <row r="21" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="63" t="s">
         <v>245</v>
       </c>
       <c r="C21" s="49"/>
     </row>
     <row r="22" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="63" t="s">
         <v>246</v>
       </c>
       <c r="C22" s="49"/>
     </row>
     <row r="23" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="63" t="s">
         <v>247</v>
       </c>
       <c r="C23" s="49"/>
     </row>
     <row r="24" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="63" t="s">
         <v>248</v>
       </c>
       <c r="C24" s="49"/>
     </row>
     <row r="25" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="63" t="s">
         <v>250</v>
       </c>
-      <c r="C25" s="62"/>
+      <c r="C25" s="65"/>
     </row>
     <row r="26" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="63" t="s">
         <v>249</v>
       </c>
       <c r="C26" s="49"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1">
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="64"/>
+      <c r="C28" s="67"/>
     </row>
     <row r="29" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="63" t="s">
         <v>251</v>
       </c>
       <c r="C29" s="49"/>
     </row>
     <row r="30" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="63" t="s">
         <v>252</v>
       </c>
       <c r="C30" s="49"/>
     </row>
     <row r="31" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="63" t="s">
         <v>254</v>
       </c>
-      <c r="C31" s="62"/>
+      <c r="C31" s="65"/>
     </row>
     <row r="32" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="63" t="s">
         <v>255</v>
       </c>
-      <c r="C32" s="62"/>
+      <c r="C32" s="65"/>
     </row>
     <row r="33" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B33" s="61" t="s">
+      <c r="B33" s="63" t="s">
         <v>256</v>
       </c>
-      <c r="C33" s="62"/>
+      <c r="C33" s="65"/>
     </row>
     <row r="34" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B34" s="61" t="s">
+      <c r="B34" s="63" t="s">
         <v>257</v>
       </c>
-      <c r="C34" s="62"/>
+      <c r="C34" s="65"/>
     </row>
     <row r="35" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B35" s="61" t="s">
+      <c r="B35" s="63" t="s">
         <v>253</v>
       </c>
       <c r="C35" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
@@ -13549,17 +13605,6 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13589,7 +13634,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="71" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="53"/>
@@ -13605,7 +13650,7 @@
       <c r="M2" s="53"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="70" t="s">
         <v>135</v>
       </c>
       <c r="C3" s="51"/>
@@ -13684,7 +13729,7 @@
         <v>100</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -13701,7 +13746,7 @@
         <v>281</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F6" s="5">
         <v>1</v>
@@ -13716,7 +13761,7 @@
         <v>100</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -13733,7 +13778,7 @@
         <v>282</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F7" s="5">
         <v>1</v>
@@ -13745,10 +13790,10 @@
         <v>1</v>
       </c>
       <c r="I7" s="5">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -13765,7 +13810,7 @@
         <v>283</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -13777,10 +13822,10 @@
         <v>1</v>
       </c>
       <c r="I8" s="5">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -13793,11 +13838,11 @@
       <c r="C9" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>284</v>
+      <c r="D9" s="15" t="s">
+        <v>298</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F9" s="5">
         <v>2</v>
@@ -13808,8 +13853,12 @@
       <c r="H9" s="5">
         <v>1</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
+      <c r="I9" s="5">
+        <v>100</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -13822,10 +13871,10 @@
         <v>60</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F10" s="5">
         <v>2</v>
@@ -13836,8 +13885,12 @@
       <c r="H10" s="5">
         <v>1</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="I10" s="5">
+        <v>100</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -13850,10 +13903,10 @@
         <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F11" s="5">
         <v>2</v>
@@ -13864,8 +13917,12 @@
       <c r="H11" s="5">
         <v>1</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+      <c r="I11" s="5">
+        <v>100</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -13878,10 +13935,10 @@
         <v>60</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F12" s="5">
         <v>2</v>
@@ -13892,8 +13949,12 @@
       <c r="H12" s="5">
         <v>1</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="I12" s="5">
+        <v>100</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -13906,10 +13967,10 @@
         <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F13" s="5">
         <v>2</v>
@@ -13920,8 +13981,12 @@
       <c r="H13" s="5">
         <v>1</v>
       </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="I13" s="5">
+        <v>100</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -13934,10 +13999,10 @@
         <v>278</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F14" s="5">
         <v>2</v>
@@ -13948,8 +14013,12 @@
       <c r="H14" s="5">
         <v>1</v>
       </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="I14" s="5">
+        <v>100</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -13962,10 +14031,10 @@
         <v>61</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F15" s="5">
         <v>3</v>
@@ -13990,7 +14059,7 @@
         <v>62</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>280</v>
@@ -14018,10 +14087,10 @@
         <v>63</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F17" s="5">
         <v>3</v>
@@ -14046,7 +14115,7 @@
         <v>64</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>280</v>
@@ -14070,72 +14139,72 @@
       <c r="D19" s="28"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="84" t="s">
+      <c r="B20" s="72" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="85"/>
+      <c r="C20" s="73"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="86" t="s">
+      <c r="B21" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="87"/>
+      <c r="C21" s="75"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="88" t="s">
+      <c r="B22" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="89"/>
+      <c r="C22" s="77"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="72" t="s">
+      <c r="B23" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="73"/>
+      <c r="C23" s="81"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="75"/>
+      <c r="C24" s="83"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="76" t="s">
+      <c r="B25" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="77"/>
+      <c r="C25" s="85"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="78" t="s">
+      <c r="B26" s="86" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="79"/>
+      <c r="C26" s="87"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="80" t="s">
+      <c r="B27" s="88" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="81"/>
+      <c r="C27" s="89"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="70" t="s">
+      <c r="B28" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">

--- a/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\TEAM PJT JM 2\Ssafy_We_Are\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C872331-7283-4AC7-9995-7B03AF0AB24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC353505-9614-4F8A-BC1F-7BB96E6000C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3750" yWindow="1485" windowWidth="18240" windowHeight="15345" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="300">
   <si>
     <t>실습 소재</t>
   </si>
@@ -11063,6 +11063,9 @@
       <t>구현</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
   </si>
 </sst>
 </file>
@@ -11726,19 +11729,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11752,30 +11755,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -11811,6 +11790,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13388,7 +13391,7 @@
       <c r="C2" s="53"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="65" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="44"/>
@@ -13426,13 +13429,13 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="62"/>
+      <c r="C9" s="64"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="61" t="s">
         <v>236</v>
       </c>
       <c r="C10" s="49"/>
@@ -13444,7 +13447,7 @@
       <c r="C11" s="49"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="61" t="s">
         <v>238</v>
       </c>
       <c r="C12" s="49"/>
@@ -13462,7 +13465,7 @@
       <c r="C14" s="49"/>
     </row>
     <row r="15" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B15" s="63" t="s">
+      <c r="B15" s="61" t="s">
         <v>241</v>
       </c>
       <c r="C15" s="49"/>
@@ -13481,7 +13484,7 @@
       <c r="C17" s="49"/>
     </row>
     <row r="18" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="61" t="s">
         <v>244</v>
       </c>
       <c r="C18" s="49"/>
@@ -13493,37 +13496,37 @@
       <c r="C20" s="69"/>
     </row>
     <row r="21" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B21" s="63" t="s">
+      <c r="B21" s="61" t="s">
         <v>245</v>
       </c>
       <c r="C21" s="49"/>
     </row>
     <row r="22" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="61" t="s">
         <v>246</v>
       </c>
       <c r="C22" s="49"/>
     </row>
     <row r="23" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="61" t="s">
         <v>247</v>
       </c>
       <c r="C23" s="49"/>
     </row>
     <row r="24" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B24" s="63" t="s">
+      <c r="B24" s="61" t="s">
         <v>248</v>
       </c>
       <c r="C24" s="49"/>
     </row>
     <row r="25" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="61" t="s">
         <v>250</v>
       </c>
-      <c r="C25" s="65"/>
+      <c r="C25" s="62"/>
     </row>
     <row r="26" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="61" t="s">
         <v>249</v>
       </c>
       <c r="C26" s="49"/>
@@ -13535,60 +13538,49 @@
       <c r="C28" s="67"/>
     </row>
     <row r="29" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="61" t="s">
         <v>251</v>
       </c>
       <c r="C29" s="49"/>
     </row>
     <row r="30" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="61" t="s">
         <v>252</v>
       </c>
       <c r="C30" s="49"/>
     </row>
     <row r="31" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="61" t="s">
         <v>254</v>
       </c>
-      <c r="C31" s="65"/>
+      <c r="C31" s="62"/>
     </row>
     <row r="32" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="61" t="s">
         <v>255</v>
       </c>
-      <c r="C32" s="65"/>
+      <c r="C32" s="62"/>
     </row>
     <row r="33" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="61" t="s">
         <v>256</v>
       </c>
-      <c r="C33" s="65"/>
+      <c r="C33" s="62"/>
     </row>
     <row r="34" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B34" s="63" t="s">
+      <c r="B34" s="61" t="s">
         <v>257</v>
       </c>
-      <c r="C34" s="65"/>
+      <c r="C34" s="62"/>
     </row>
     <row r="35" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B35" s="63" t="s">
+      <c r="B35" s="61" t="s">
         <v>253</v>
       </c>
       <c r="C35" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
@@ -13605,6 +13597,17 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13634,7 +13637,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="83" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="53"/>
@@ -13650,7 +13653,7 @@
       <c r="M2" s="53"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="82" t="s">
         <v>135</v>
       </c>
       <c r="C3" s="51"/>
@@ -14045,8 +14048,12 @@
       <c r="H15" s="5">
         <v>1</v>
       </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="I15" s="5">
+        <v>100</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -14073,8 +14080,12 @@
       <c r="H16" s="5">
         <v>1</v>
       </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="I16" s="5">
+        <v>80</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>299</v>
+      </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -14101,8 +14112,12 @@
       <c r="H17" s="5">
         <v>1</v>
       </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="I17" s="5">
+        <v>100</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -14129,8 +14144,12 @@
       <c r="H18" s="5">
         <v>1</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
+      <c r="I18" s="5">
+        <v>100</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -14139,72 +14158,72 @@
       <c r="D19" s="28"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="72" t="s">
+      <c r="B20" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="73"/>
+      <c r="C20" s="85"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="75"/>
+      <c r="C21" s="87"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="76" t="s">
+      <c r="B22" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="77"/>
+      <c r="C22" s="89"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="80" t="s">
+      <c r="B23" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="81"/>
+      <c r="C23" s="73"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="82" t="s">
+      <c r="B24" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="83"/>
+      <c r="C24" s="75"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="84" t="s">
+      <c r="B25" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="85"/>
+      <c r="C25" s="77"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="86" t="s">
+      <c r="B26" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="87"/>
+      <c r="C26" s="79"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="89"/>
+      <c r="C27" s="81"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="78" t="s">
+      <c r="B28" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="79"/>
+      <c r="C28" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">

--- a/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\TEAM PJT JM 2\Ssafy_We_Are\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\나의_SSAFY_이야기\AI_온보딩_[팀_프로젝트]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC353505-9614-4F8A-BC1F-7BB96E6000C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7CCB1C-83D8-44FD-BA66-5D394439E2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3555" yWindow="1305" windowWidth="28800" windowHeight="15345" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -11729,19 +11729,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11755,6 +11755,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -11790,30 +11814,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13391,7 +13391,7 @@
       <c r="C2" s="53"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="64" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="44"/>
@@ -13429,13 +13429,13 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="64"/>
+      <c r="C9" s="62"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="63" t="s">
         <v>236</v>
       </c>
       <c r="C10" s="49"/>
@@ -13447,7 +13447,7 @@
       <c r="C11" s="49"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="63" t="s">
         <v>238</v>
       </c>
       <c r="C12" s="49"/>
@@ -13465,7 +13465,7 @@
       <c r="C14" s="49"/>
     </row>
     <row r="15" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="63" t="s">
         <v>241</v>
       </c>
       <c r="C15" s="49"/>
@@ -13484,7 +13484,7 @@
       <c r="C17" s="49"/>
     </row>
     <row r="18" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="63" t="s">
         <v>244</v>
       </c>
       <c r="C18" s="49"/>
@@ -13496,37 +13496,37 @@
       <c r="C20" s="69"/>
     </row>
     <row r="21" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="63" t="s">
         <v>245</v>
       </c>
       <c r="C21" s="49"/>
     </row>
     <row r="22" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="63" t="s">
         <v>246</v>
       </c>
       <c r="C22" s="49"/>
     </row>
     <row r="23" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="63" t="s">
         <v>247</v>
       </c>
       <c r="C23" s="49"/>
     </row>
     <row r="24" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="63" t="s">
         <v>248</v>
       </c>
       <c r="C24" s="49"/>
     </row>
     <row r="25" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="63" t="s">
         <v>250</v>
       </c>
-      <c r="C25" s="62"/>
+      <c r="C25" s="65"/>
     </row>
     <row r="26" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="63" t="s">
         <v>249</v>
       </c>
       <c r="C26" s="49"/>
@@ -13538,49 +13538,60 @@
       <c r="C28" s="67"/>
     </row>
     <row r="29" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="63" t="s">
         <v>251</v>
       </c>
       <c r="C29" s="49"/>
     </row>
     <row r="30" spans="1:3" ht="25.5" customHeight="1">
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="63" t="s">
         <v>252</v>
       </c>
       <c r="C30" s="49"/>
     </row>
     <row r="31" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="63" t="s">
         <v>254</v>
       </c>
-      <c r="C31" s="62"/>
+      <c r="C31" s="65"/>
     </row>
     <row r="32" spans="1:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="63" t="s">
         <v>255</v>
       </c>
-      <c r="C32" s="62"/>
+      <c r="C32" s="65"/>
     </row>
     <row r="33" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B33" s="61" t="s">
+      <c r="B33" s="63" t="s">
         <v>256</v>
       </c>
-      <c r="C33" s="62"/>
+      <c r="C33" s="65"/>
     </row>
     <row r="34" spans="2:3" s="28" customFormat="1" ht="25.5" customHeight="1">
-      <c r="B34" s="61" t="s">
+      <c r="B34" s="63" t="s">
         <v>257</v>
       </c>
-      <c r="C34" s="62"/>
+      <c r="C34" s="65"/>
     </row>
     <row r="35" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B35" s="61" t="s">
+      <c r="B35" s="63" t="s">
         <v>253</v>
       </c>
       <c r="C35" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
@@ -13597,17 +13608,6 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13637,7 +13637,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="71" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="53"/>
@@ -13653,7 +13653,7 @@
       <c r="M2" s="53"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="70" t="s">
         <v>135</v>
       </c>
       <c r="C3" s="51"/>
@@ -14158,72 +14158,72 @@
       <c r="D19" s="28"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="84" t="s">
+      <c r="B20" s="72" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="85"/>
+      <c r="C20" s="73"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="86" t="s">
+      <c r="B21" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="87"/>
+      <c r="C21" s="75"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="88" t="s">
+      <c r="B22" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="89"/>
+      <c r="C22" s="77"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="72" t="s">
+      <c r="B23" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="73"/>
+      <c r="C23" s="81"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="75"/>
+      <c r="C24" s="83"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="76" t="s">
+      <c r="B25" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="77"/>
+      <c r="C25" s="85"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="78" t="s">
+      <c r="B26" s="86" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="79"/>
+      <c r="C26" s="87"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="80" t="s">
+      <c r="B27" s="88" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="81"/>
+      <c r="C27" s="89"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="70" t="s">
+      <c r="B28" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">

--- a/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\TEAM PJT JM 2\Ssafy_We_Are\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC353505-9614-4F8A-BC1F-7BB96E6000C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAEE8D1-A82B-443D-9E0C-5A177C981D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="299">
   <si>
     <t>실습 소재</t>
   </si>
@@ -11063,9 +11063,6 @@
       <t>구현</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>진행중</t>
   </si>
 </sst>
 </file>
@@ -14081,10 +14078,10 @@
         <v>1</v>
       </c>
       <c r="I16" s="5">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
